--- a/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v7.xlsx
+++ b/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v7.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\docs\migration-orders\prompt-to-claude-code\antigravity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\docs\migration-orders\davin-operational-manual\antigravity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3C8BE4-C59A-4C7A-81A2-68F9A4A36BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F313614-7818-4F2D-8217-936EB8108192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3955,11 +3955,6 @@
 (เมื่อ CONFIRM ผ่านครบทุกข้อแล้ว ให้พิมพ์: Go.)</t>
   </si>
   <si>
-    <t>Wrap up per EXECUTOR-PROTOCOL §3: tests + results, fill Deviations, update the artifacts, harvest any lesson into LESSONS-LEARNED.md, then PRE-DRAFT session 4A-12's order and show it to me. Confirm shadow/mirror-run STARTED and the source files are now CC-F frozen — state the exact 48h end time.
-— จากนั้นส่งคำสั่ง WAIT ต่อทันที —
-Confirm the clock: what started, exact end date/time UTC, what to watch, what failure ends the wait early. Put all four in CLAUDE.md under "Waiting on".</t>
-  </si>
-  <si>
     <t>CUTOVER slice 5: core เลิกอ่าน Subscription ตรงๆ + เริ่มนาฬิกาเสถียรภาพ 30 วันของ money-service</t>
   </si>
   <si>
@@ -5062,6 +5057,11 @@
   <si>
     <t>Read CLAUDE.md and docs/migration-orders/EXECUTOR-PROTOCOL.md. CONFIRM the APPROVED order for session 4A-10a against the current codebase AND runtime state, and show me: what changed since drafting, the "done when" checks, and any failing entry criterion. Do not execute until I say go. First: the shadow/replay diff — total compared, match rate, EVERY mismatch with your explanation.
 (เมื่อ CONFIRM ผ่านครบทุกข้อแล้ว ให้พิมพ์: Go.)</t>
+  </si>
+  <si>
+    <t>Wrap up per EXECUTOR-PROTOCOL §3: tests + results, fill Deviations, update the artifacts, harvest any lesson into LESSONS-LEARNED.md, then PRE-DRAFT session 4A-12's order and show it to me. Confirm shadow/mirror-run STARTED and the source files are now CC-F frozen — state the exact 48h end time. 
+— จากนั้นส่งคำสั่ง WAIT ต่อทันที —
+Confirm the clock: what started, exact end date/time UTC, what to watch, what failure ends the wait early. Put all four in CLAUDE.md under "Waiting on".</t>
   </si>
 </sst>
 </file>
@@ -5242,7 +5242,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5297,12 +5297,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
       </patternFill>
     </fill>
@@ -5324,6 +5318,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7F0FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -5513,7 +5519,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -5545,35 +5550,35 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5582,25 +5587,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5609,42 +5626,26 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -5663,31 +5664,44 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5695,46 +5709,36 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6282,7 +6286,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="54" t="s">
         <v>36</v>
       </c>
     </row>
@@ -6386,7 +6390,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="55" t="s">
+      <c r="B38" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -6446,12 +6450,12 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="58" t="s">
+      <c r="B46" s="57" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="61" t="s">
+      <c r="B48" s="60" t="s">
         <v>69</v>
       </c>
     </row>
@@ -6533,7 +6537,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="62" t="s">
+      <c r="B58" s="61" t="s">
         <v>87</v>
       </c>
     </row>
@@ -6573,10 +6577,10 @@
         <v>503</v>
       </c>
       <c r="E1" s="17" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>1481</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>1482</v>
       </c>
       <c r="G1" s="17" t="s">
         <v>29</v>
@@ -6596,13 +6600,13 @@
         <v>444</v>
       </c>
       <c r="E2" s="18" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>1483</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="G2" s="18" t="s">
         <v>1484</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>1485</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>1072</v>
@@ -6622,10 +6626,10 @@
         <v>448</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G3" t="s">
         <v>1078</v>
@@ -6645,10 +6649,10 @@
         <v>448</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6665,10 +6669,10 @@
         <v>448</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6685,10 +6689,10 @@
         <v>448</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="33" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6705,10 +6709,10 @@
         <v>451</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6725,10 +6729,10 @@
         <v>448</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="33" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6745,10 +6749,10 @@
         <v>448</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="33" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6765,10 +6769,10 @@
         <v>448</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="33" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6785,13 +6789,13 @@
         <v>457</v>
       </c>
       <c r="E11" s="37" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G11" s="37" t="s">
         <v>1488</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>1484</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="33" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6808,10 +6812,10 @@
         <v>448</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6828,10 +6832,10 @@
         <v>448</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6848,10 +6852,10 @@
         <v>448</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6868,10 +6872,10 @@
         <v>448</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="9" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6888,10 +6892,10 @@
         <v>451</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6908,10 +6912,10 @@
         <v>448</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6928,10 +6932,10 @@
         <v>448</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6948,10 +6952,10 @@
         <v>448</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6968,10 +6972,10 @@
         <v>448</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -6988,17 +6992,17 @@
         <v>451</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="18">
         <v>21</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="46" t="s">
         <v>654</v>
       </c>
       <c r="C22" s="18" t="s">
@@ -7008,40 +7012,40 @@
         <v>454</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="18">
         <v>22</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="50" t="s">
         <v>181</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="48" t="s">
         <v>457</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="18">
         <v>23</v>
       </c>
-      <c r="B24" s="48" t="s">
+      <c r="B24" s="47" t="s">
         <v>668</v>
       </c>
       <c r="C24" s="18" t="s">
@@ -7051,17 +7055,17 @@
         <v>454</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="18">
         <v>24</v>
       </c>
-      <c r="B25" s="48" t="s">
+      <c r="B25" s="47" t="s">
         <v>185</v>
       </c>
       <c r="C25" s="18" t="s">
@@ -7071,17 +7075,17 @@
         <v>457</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="18">
         <v>25</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="46" t="s">
         <v>681</v>
       </c>
       <c r="C26" s="18" t="s">
@@ -7091,286 +7095,286 @@
         <v>454</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="18">
         <v>26</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="50" t="s">
         <v>112</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="D27" s="49" t="s">
+      <c r="D27" s="48" t="s">
         <v>451</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G27" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="18">
         <v>27</v>
       </c>
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="50" t="s">
         <v>117</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="D28" s="49" t="s">
+      <c r="D28" s="48" t="s">
         <v>457</v>
       </c>
       <c r="E28" s="18" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G28" t="s">
         <v>1495</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>1484</v>
-      </c>
-      <c r="G28" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="18">
         <v>28</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="50" t="s">
         <v>122</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="48" t="s">
         <v>451</v>
       </c>
       <c r="E29" s="18" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G29" t="s">
         <v>1497</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>1484</v>
-      </c>
-      <c r="G29" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="18">
         <v>29</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="50" t="s">
         <v>127</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="D30" s="49" t="s">
+      <c r="D30" s="48" t="s">
         <v>448</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G30" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="18">
         <v>30</v>
       </c>
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="50" t="s">
         <v>132</v>
       </c>
       <c r="C31" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="D31" s="49" t="s">
+      <c r="D31" s="48" t="s">
         <v>454</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G31" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="18">
         <v>30</v>
       </c>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="50" t="s">
         <v>137</v>
       </c>
       <c r="C32" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="D32" s="49" t="s">
+      <c r="D32" s="48" t="s">
         <v>454</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G32" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="18">
         <v>31</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="50" t="s">
         <v>139</v>
       </c>
       <c r="C33" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="D33" s="49" t="s">
+      <c r="D33" s="48" t="s">
         <v>448</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G33" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="18">
         <v>32</v>
       </c>
-      <c r="B34" s="51" t="s">
+      <c r="B34" s="50" t="s">
         <v>142</v>
       </c>
       <c r="C34" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="D34" s="49" t="s">
+      <c r="D34" s="48" t="s">
         <v>454</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G34" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="18">
         <v>33</v>
       </c>
-      <c r="B35" s="51" t="s">
+      <c r="B35" s="50" t="s">
         <v>145</v>
       </c>
       <c r="C35" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="D35" s="49" t="s">
+      <c r="D35" s="48" t="s">
         <v>454</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G35" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="18">
         <v>34</v>
       </c>
-      <c r="B36" s="51" t="s">
+      <c r="B36" s="50" t="s">
         <v>148</v>
       </c>
       <c r="C36" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="D36" s="49" t="s">
+      <c r="D36" s="48" t="s">
         <v>457</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G36" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="18">
         <v>35</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B37" s="50" t="s">
         <v>218</v>
       </c>
       <c r="C37" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="D37" s="49" t="s">
+      <c r="D37" s="48" t="s">
         <v>461</v>
       </c>
       <c r="E37" s="18" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F37" s="18" t="s">
         <v>1505</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="G37" t="s">
         <v>1506</v>
-      </c>
-      <c r="G37" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="18">
         <v>36</v>
       </c>
-      <c r="B38" s="51" t="s">
+      <c r="B38" s="50" t="s">
         <v>151</v>
       </c>
       <c r="C38" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="D38" s="49" t="s">
+      <c r="D38" s="48" t="s">
         <v>457</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G38" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7387,17 +7391,17 @@
         <v>448</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="18">
         <v>38</v>
       </c>
-      <c r="B40" s="48" t="s">
+      <c r="B40" s="47" t="s">
         <v>794</v>
       </c>
       <c r="C40" s="18" t="s">
@@ -7407,40 +7411,40 @@
         <v>454</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="18">
         <v>39</v>
       </c>
-      <c r="B41" s="52" t="s">
+      <c r="B41" s="51" t="s">
         <v>799</v>
       </c>
       <c r="C41" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="D41" s="49" t="s">
+      <c r="D41" s="48" t="s">
         <v>461</v>
       </c>
       <c r="E41" s="18" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F41" s="18" t="s">
         <v>1509</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="G41" s="18" t="s">
         <v>1510</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="18">
         <v>40</v>
       </c>
-      <c r="B42" s="48" t="s">
+      <c r="B42" s="47" t="s">
         <v>806</v>
       </c>
       <c r="C42" s="18" t="s">
@@ -7450,40 +7454,40 @@
         <v>457</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="18">
         <v>41</v>
       </c>
-      <c r="B43" s="52" t="s">
+      <c r="B43" s="51" t="s">
         <v>813</v>
       </c>
       <c r="C43" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="D43" s="49" t="s">
+      <c r="D43" s="48" t="s">
         <v>461</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="F43" s="18" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G43" s="18" t="s">
         <v>1512</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="18">
         <v>42</v>
       </c>
-      <c r="B44" s="47" t="s">
+      <c r="B44" s="46" t="s">
         <v>818</v>
       </c>
       <c r="C44" s="18" t="s">
@@ -7493,33 +7497,33 @@
         <v>454</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="18">
         <v>43</v>
       </c>
-      <c r="B45" s="50" t="s">
+      <c r="B45" s="49" t="s">
         <v>823</v>
       </c>
       <c r="C45" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="D45" s="49" t="s">
+      <c r="D45" s="48" t="s">
         <v>457</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7536,10 +7540,10 @@
         <v>448</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="F46" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7556,10 +7560,10 @@
         <v>454</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7576,10 +7580,10 @@
         <v>457</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7596,10 +7600,10 @@
         <v>448</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7616,10 +7620,10 @@
         <v>454</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="F50" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7636,10 +7640,10 @@
         <v>457</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7656,10 +7660,10 @@
         <v>454</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7676,10 +7680,10 @@
         <v>457</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7696,10 +7700,10 @@
         <v>454</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7716,10 +7720,10 @@
         <v>457</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7736,10 +7740,10 @@
         <v>454</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F56" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7756,10 +7760,10 @@
         <v>457</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F57" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7776,10 +7780,10 @@
         <v>454</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F58" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7796,10 +7800,10 @@
         <v>457</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F59" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7816,10 +7820,10 @@
         <v>454</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F60" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7836,10 +7840,10 @@
         <v>457</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F61" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7856,10 +7860,10 @@
         <v>454</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7876,10 +7880,10 @@
         <v>457</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7896,10 +7900,10 @@
         <v>448</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7916,10 +7920,10 @@
         <v>454</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F65" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7936,13 +7940,13 @@
         <v>461</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="F66" s="18" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G66" s="18" t="s">
         <v>1517</v>
-      </c>
-      <c r="G66" s="18" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7959,10 +7963,10 @@
         <v>457</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F67" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7979,13 +7983,13 @@
         <v>461</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="F68" s="18" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G68" s="18" t="s">
         <v>1519</v>
-      </c>
-      <c r="G68" s="18" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8002,13 +8006,13 @@
         <v>457</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F69" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8025,13 +8029,13 @@
         <v>448</v>
       </c>
       <c r="E70" s="18" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G70" s="18" t="s">
         <v>1522</v>
-      </c>
-      <c r="F70" s="18" t="s">
-        <v>1484</v>
-      </c>
-      <c r="G70" s="18" t="s">
-        <v>1523</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8048,10 +8052,10 @@
         <v>448</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="F71" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8068,10 +8072,10 @@
         <v>448</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="F72" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8088,10 +8092,10 @@
         <v>448</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="F73" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8108,13 +8112,13 @@
         <v>451</v>
       </c>
       <c r="E74" s="18" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G74" s="18" t="s">
         <v>1524</v>
-      </c>
-      <c r="F74" s="18" t="s">
-        <v>1484</v>
-      </c>
-      <c r="G74" s="18" t="s">
-        <v>1525</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8131,10 +8135,10 @@
         <v>448</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="F75" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8151,10 +8155,10 @@
         <v>448</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="F76" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8171,10 +8175,10 @@
         <v>448</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="F77" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8191,10 +8195,10 @@
         <v>448</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="F78" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8211,10 +8215,10 @@
         <v>448</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="F79" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8231,10 +8235,10 @@
         <v>448</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="F80" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8251,10 +8255,10 @@
         <v>448</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="F81" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8271,10 +8275,10 @@
         <v>457</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F82" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8291,10 +8295,10 @@
         <v>448</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="F83" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8311,10 +8315,10 @@
         <v>448</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="F84" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8331,10 +8335,10 @@
         <v>448</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="F85" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8351,10 +8355,10 @@
         <v>457</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F86" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8371,10 +8375,10 @@
         <v>448</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="F87" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8391,10 +8395,10 @@
         <v>448</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="F88" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8411,10 +8415,10 @@
         <v>448</v>
       </c>
       <c r="E89" s="18" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="F89" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -8431,165 +8435,165 @@
         <v>457</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F90" s="18" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="92" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="93" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="19" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="18" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="18" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="18" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="18" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="18" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="18" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="18" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="18" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="18" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="18" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="18" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="18" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="140.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="18" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="109.2" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="108" spans="1:3" ht="96.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="19" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="18" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="95.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="18" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="90.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="18" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="172.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="18" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="113" spans="1:1" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="18" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="114" spans="1:1" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="18" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="115" spans="1:1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="18" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
   </sheetData>
@@ -8619,170 +8623,170 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>1559</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>1560</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>1561</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>1562</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>1563</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>1564</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>1565</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="I12" s="9" t="s">
         <v>1566</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="J12" s="9" t="s">
         <v>1567</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>1568</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="9" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>1569</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>1570</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>1571</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>1572</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>1573</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>1574</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>1575</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="I13" s="9" t="s">
+        <v>1574</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>1576</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>1575</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>1577</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="9" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>1578</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>1579</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>1580</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>1581</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>1582</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>1583</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>1584</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="I14" s="9" t="s">
         <v>1585</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="J14" s="9" t="s">
         <v>1586</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>1587</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="9" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>1588</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>1589</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>1590</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>1591</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
+        <v>1583</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>1592</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>1584</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>1585</v>
-      </c>
-      <c r="I15" s="9" t="s">
+      <c r="J15" s="9" t="s">
         <v>1593</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="9" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -8796,98 +8800,98 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="9" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>1596</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>1597</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>1583</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>1598</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>1592</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>1584</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>1585</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>1593</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>1599</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="9" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>1600</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="D18" s="9" t="s">
         <v>1601</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="E18" s="9" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>1583</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>1602</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>1592</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>1584</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>1585</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>1593</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>1603</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="9" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>1604</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="D19" s="9" t="s">
         <v>1605</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="E19" s="9" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>1583</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>1606</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>1592</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>1584</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>1585</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>1593</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>1607</v>
       </c>
     </row>
   </sheetData>
@@ -8902,27 +8906,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
   </sheetData>
@@ -8945,489 +8949,489 @@
       <c r="A1" s="100" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
     </row>
     <row r="2" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="109" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
     </row>
     <row r="4" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="95" t="s">
+      <c r="A4" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
     </row>
     <row r="5" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="70" t="s">
+      <c r="E5" s="69" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="70" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="D6" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="72" t="s">
+      <c r="E6" s="71" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="72" t="s">
+      <c r="E7" s="71" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="107" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
     </row>
     <row r="10" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="69" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="73" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="73" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="73" t="s">
         <v>115</v>
       </c>
-      <c r="E11" s="74" t="s">
+      <c r="E11" s="73" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="74" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="75" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="75" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="76" t="s">
+      <c r="D12" s="75" t="s">
         <v>120</v>
       </c>
-      <c r="E12" s="76" t="s">
+      <c r="E12" s="75" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="76" t="s">
+      <c r="B13" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="76" t="s">
+      <c r="C13" s="75" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="76" t="s">
+      <c r="D13" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E13" s="76" t="s">
+      <c r="E13" s="75" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="75" t="s">
+      <c r="A14" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="75" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="75" t="s">
         <v>130</v>
       </c>
-      <c r="E14" s="76" t="s">
+      <c r="E14" s="75" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="75" t="s">
+      <c r="A15" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="76" t="s">
+      <c r="B15" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="76" t="s">
+      <c r="C15" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="D15" s="76" t="s">
+      <c r="D15" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="E15" s="76" t="s">
+      <c r="E15" s="75" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="75" t="s">
+      <c r="A16" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="B16" s="76" t="s">
+      <c r="B16" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="E16" s="76" t="s">
+      <c r="E16" s="75" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="72" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="74" t="s">
+      <c r="B17" s="73" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="74" t="s">
+      <c r="C17" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="73" t="s">
         <v>141</v>
       </c>
-      <c r="E17" s="74" t="s">
+      <c r="E17" s="73" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="75" t="s">
+      <c r="A18" s="74" t="s">
         <v>142</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="75" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="75" t="s">
         <v>144</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="75" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="75" t="s">
+      <c r="A19" s="74" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="75" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="76" t="s">
+      <c r="C19" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="76" t="s">
+      <c r="D19" s="75" t="s">
         <v>147</v>
       </c>
-      <c r="E19" s="76" t="s">
+      <c r="E19" s="75" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="71" t="s">
+      <c r="A20" s="70" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="71" t="s">
         <v>149</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="71" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="72" t="s">
+      <c r="D20" s="71" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="72" t="s">
+      <c r="E20" s="71" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="76" t="s">
+      <c r="B21" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="C21" s="76" t="s">
+      <c r="C21" s="75" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="76" t="s">
+      <c r="D21" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="E21" s="76" t="s">
+      <c r="E21" s="75" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="C22" s="78" t="s">
+      <c r="C22" s="77" t="s">
         <v>129</v>
       </c>
-      <c r="D22" s="78" t="s">
+      <c r="D22" s="77" t="s">
         <v>157</v>
       </c>
-      <c r="E22" s="78" t="s">
+      <c r="E22" s="77" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="100.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="77" t="s">
+      <c r="A23" s="76" t="s">
         <v>158</v>
       </c>
-      <c r="B23" s="78" t="s">
+      <c r="B23" s="77" t="s">
         <v>159</v>
       </c>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78" t="s">
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="96"/>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
+      <c r="A24" s="101"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="79" t="s">
+      <c r="A25" s="78" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="70" t="s">
+      <c r="A26" s="69" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="103" t="s">
+      <c r="B26" s="104" t="s">
         <v>163</v>
       </c>
-      <c r="C26" s="103" t="s">
+      <c r="C26" s="104" t="s">
         <v>164</v>
       </c>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
     </row>
     <row r="27" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="75" t="s">
+      <c r="A27" s="74" t="s">
         <v>165</v>
       </c>
-      <c r="B27" s="97" t="s">
+      <c r="B27" s="105" t="s">
         <v>166</v>
       </c>
-      <c r="C27" s="98"/>
-      <c r="D27" s="97" t="s">
+      <c r="C27" s="106"/>
+      <c r="D27" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="E27" s="98"/>
+      <c r="E27" s="106"/>
     </row>
     <row r="28" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="75" t="s">
+      <c r="A28" s="74" t="s">
         <v>168</v>
       </c>
-      <c r="B28" s="97" t="s">
+      <c r="B28" s="105" t="s">
         <v>169</v>
       </c>
-      <c r="C28" s="98"/>
-      <c r="D28" s="97" t="s">
+      <c r="C28" s="106"/>
+      <c r="D28" s="105" t="s">
         <v>170</v>
       </c>
-      <c r="E28" s="98"/>
+      <c r="E28" s="106"/>
     </row>
     <row r="29" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="75" t="s">
+      <c r="A29" s="74" t="s">
         <v>171</v>
       </c>
-      <c r="B29" s="97" t="s">
+      <c r="B29" s="105" t="s">
         <v>172</v>
       </c>
-      <c r="C29" s="98"/>
-      <c r="D29" s="97" t="s">
+      <c r="C29" s="106"/>
+      <c r="D29" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="E29" s="98"/>
+      <c r="E29" s="106"/>
     </row>
     <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="75" t="s">
+      <c r="A30" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="B30" s="76" t="s">
+      <c r="B30" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="C30" s="80"/>
-      <c r="D30" s="76" t="s">
+      <c r="C30" s="79"/>
+      <c r="D30" s="75" t="s">
         <v>176</v>
       </c>
-      <c r="E30" s="80"/>
+      <c r="E30" s="79"/>
     </row>
     <row r="31" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="96"/>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="82" t="s">
+      <c r="A32" s="81" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="69" t="s">
         <v>178</v>
       </c>
-      <c r="C33" s="70" t="s">
+      <c r="C33" s="69" t="s">
         <v>179</v>
       </c>
-      <c r="D33" s="70" t="s">
+      <c r="D33" s="69" t="s">
         <v>180</v>
       </c>
-      <c r="E33" s="70"/>
+      <c r="E33" s="69"/>
     </row>
     <row r="34" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="73" t="s">
+      <c r="A34" s="72" t="s">
         <v>181</v>
       </c>
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="C34" s="74" t="s">
+      <c r="C34" s="73" t="s">
         <v>183</v>
       </c>
-      <c r="D34" s="74" t="s">
+      <c r="D34" s="73" t="s">
         <v>184</v>
       </c>
-      <c r="E34" s="74"/>
+      <c r="E34" s="73"/>
     </row>
     <row r="35" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="74" t="s">
         <v>185</v>
       </c>
-      <c r="B35" s="76" t="s">
+      <c r="B35" s="75" t="s">
         <v>186</v>
       </c>
-      <c r="C35" s="76" t="s">
+      <c r="C35" s="75" t="s">
         <v>187</v>
       </c>
-      <c r="D35" s="76" t="s">
+      <c r="D35" s="75" t="s">
         <v>188</v>
       </c>
-      <c r="E35" s="76"/>
+      <c r="E35" s="75"/>
     </row>
     <row r="36" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="71" t="s">
+      <c r="A36" s="70" t="s">
         <v>189</v>
       </c>
-      <c r="B36" s="72" t="s">
+      <c r="B36" s="71" t="s">
         <v>190</v>
       </c>
-      <c r="C36" s="72" t="s">
+      <c r="C36" s="71" t="s">
         <v>191</v>
       </c>
-      <c r="D36" s="72" t="s">
+      <c r="D36" s="71" t="s">
         <v>192</v>
       </c>
-      <c r="E36" s="72"/>
+      <c r="E36" s="71"/>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="101" t="s">
+      <c r="A37" s="102" t="s">
         <v>193</v>
       </c>
-      <c r="B37" s="102" t="s">
+      <c r="B37" s="103" t="s">
         <v>194</v>
       </c>
-      <c r="C37" s="102" t="s">
+      <c r="C37" s="103" t="s">
         <v>195</v>
       </c>
-      <c r="D37" s="102" t="s">
+      <c r="D37" s="103" t="s">
         <v>196</v>
       </c>
-      <c r="E37" s="102"/>
+      <c r="E37" s="103"/>
     </row>
     <row r="38" spans="1:5" ht="230.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="81" t="s">
+      <c r="A38" s="80" t="s">
         <v>197</v>
       </c>
     </row>
@@ -9466,554 +9470,554 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="110" t="s">
         <v>198</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="111" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
     </row>
     <row r="4" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="111" t="s">
+      <c r="A4" s="113" t="s">
         <v>200</v>
       </c>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
     </row>
     <row r="5" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="111" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
     </row>
     <row r="6" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="107" t="s">
+      <c r="A6" s="111" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="96"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
+      <c r="B6" s="101"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
     </row>
     <row r="7" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="107" t="s">
+      <c r="A7" s="111" t="s">
         <v>203</v>
       </c>
-      <c r="B7" s="96"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
+      <c r="B7" s="101"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="101"/>
     </row>
     <row r="8" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="107" t="s">
+      <c r="A8" s="111" t="s">
         <v>204</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
     </row>
     <row r="10" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="112" t="s">
+      <c r="A10" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
     </row>
     <row r="11" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="D11" s="63" t="s">
+      <c r="D11" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="62" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="64" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="64" t="s">
         <v>210</v>
       </c>
-      <c r="D13" s="65" t="s">
+      <c r="D13" s="64" t="s">
         <v>211</v>
       </c>
-      <c r="E13" s="65" t="s">
+      <c r="E13" s="64" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="64" t="s">
         <v>212</v>
       </c>
-      <c r="D14" s="65" t="s">
+      <c r="D14" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="E14" s="65" t="s">
+      <c r="E14" s="64" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="75" t="s">
+      <c r="A15" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="76" t="s">
+      <c r="B15" s="75" t="s">
         <v>137</v>
       </c>
-      <c r="C15" s="76" t="s">
+      <c r="C15" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="D15" s="76" t="s">
+      <c r="D15" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="E15" s="76" t="s">
+      <c r="E15" s="75" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="65" t="s">
         <v>139</v>
       </c>
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="66" t="s">
         <v>213</v>
       </c>
-      <c r="C16" s="67" t="s">
+      <c r="C16" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="E16" s="67" t="s">
+      <c r="E16" s="66" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="B17" s="65" t="s">
+      <c r="B17" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="65" t="s">
+      <c r="C17" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="65" t="s">
+      <c r="D17" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="E17" s="65" t="s">
+      <c r="E17" s="64" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="B18" s="65" t="s">
+      <c r="B18" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="65" t="s">
+      <c r="C18" s="64" t="s">
         <v>216</v>
       </c>
-      <c r="D18" s="65" t="s">
+      <c r="D18" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="E18" s="65" t="s">
+      <c r="E18" s="64" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="67" t="s">
         <v>148</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="69" t="s">
+      <c r="C19" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="D19" s="69" t="s">
+      <c r="D19" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="E19" s="69" t="s">
+      <c r="E19" s="68" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="67" t="s">
         <v>218</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="68" t="s">
         <v>219</v>
       </c>
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="68" t="s">
         <v>220</v>
       </c>
-      <c r="D20" s="69" t="s">
+      <c r="D20" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="E20" s="69" t="s">
+      <c r="E20" s="68" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="65" t="s">
+      <c r="B21" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="D21" s="65" t="s">
+      <c r="D21" s="64" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="65" t="s">
+      <c r="E21" s="64" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="109"/>
-      <c r="B22" s="110"/>
-      <c r="C22" s="110" t="s">
+      <c r="A22" s="114"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="115" t="s">
         <v>223</v>
       </c>
-      <c r="D22" s="110" t="s">
+      <c r="D22" s="115" t="s">
         <v>224</v>
       </c>
-      <c r="E22" s="110" t="s">
+      <c r="E22" s="115" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="100.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="83" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="96"/>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
+      <c r="A24" s="101"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
     </row>
     <row r="25" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="60" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="88" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="63" t="s">
+      <c r="A26" s="62" t="s">
         <v>228</v>
       </c>
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="62" t="s">
         <v>229</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="62" t="s">
         <v>230</v>
       </c>
-      <c r="D26" s="63" t="s">
+      <c r="D26" s="62" t="s">
         <v>231</v>
       </c>
-      <c r="E26" s="63" t="s">
+      <c r="E26" s="62" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="88" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="68" t="s">
+      <c r="A27" s="67" t="s">
         <v>233</v>
       </c>
-      <c r="B27" s="69" t="s">
+      <c r="B27" s="68" t="s">
         <v>234</v>
       </c>
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="68" t="s">
         <v>235</v>
       </c>
-      <c r="D27" s="69" t="s">
+      <c r="D27" s="68" t="s">
         <v>236</v>
       </c>
-      <c r="E27" s="69" t="s">
+      <c r="E27" s="68" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="113" t="s">
+      <c r="A28" s="117" t="s">
         <v>237</v>
       </c>
-      <c r="B28" s="114" t="s">
+      <c r="B28" s="118" t="s">
         <v>238</v>
       </c>
-      <c r="C28" s="114" t="s">
+      <c r="C28" s="118" t="s">
         <v>239</v>
       </c>
-      <c r="D28" s="114" t="s">
+      <c r="D28" s="118" t="s">
         <v>240</v>
       </c>
-      <c r="E28" s="114" t="s">
+      <c r="E28" s="118" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="107" t="s">
+      <c r="A29" s="111" t="s">
         <v>241</v>
       </c>
-      <c r="B29" s="96"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="96"/>
-      <c r="E29" s="96"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="101"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="101"/>
     </row>
     <row r="30" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="83" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="96"/>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
     </row>
     <row r="32" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="85" t="s">
+      <c r="A32" s="84" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="62" t="s">
         <v>244</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="62" t="s">
         <v>245</v>
       </c>
-      <c r="C33" s="63" t="s">
+      <c r="C33" s="62" t="s">
         <v>246</v>
       </c>
-      <c r="D33" s="63" t="s">
+      <c r="D33" s="62" t="s">
         <v>247</v>
       </c>
-      <c r="E33" s="63" t="s">
+      <c r="E33" s="62" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="64" t="s">
+      <c r="A34" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="B34" s="65" t="s">
+      <c r="B34" s="64" t="s">
         <v>248</v>
       </c>
-      <c r="C34" s="65" t="s">
+      <c r="C34" s="64" t="s">
         <v>249</v>
       </c>
-      <c r="D34" s="65" t="s">
+      <c r="D34" s="64" t="s">
         <v>250</v>
       </c>
-      <c r="E34" s="65" t="s">
+      <c r="E34" s="64" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="64" t="s">
+      <c r="A35" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="B35" s="65" t="s">
+      <c r="B35" s="64" t="s">
         <v>251</v>
       </c>
-      <c r="C35" s="65" t="s">
+      <c r="C35" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="D35" s="65" t="s">
+      <c r="D35" s="64" t="s">
         <v>253</v>
       </c>
-      <c r="E35" s="65" t="s">
+      <c r="E35" s="64" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="64" t="s">
+      <c r="A36" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="65" t="s">
+      <c r="B36" s="64" t="s">
         <v>255</v>
       </c>
-      <c r="C36" s="65" t="s">
+      <c r="C36" s="64" t="s">
         <v>256</v>
       </c>
-      <c r="D36" s="65" t="s">
+      <c r="D36" s="64" t="s">
         <v>257</v>
       </c>
-      <c r="E36" s="65" t="s">
+      <c r="E36" s="64" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="100.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="64" t="s">
+      <c r="A37" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="65" t="s">
+      <c r="B37" s="64" t="s">
         <v>258</v>
       </c>
-      <c r="C37" s="65" t="s">
+      <c r="C37" s="64" t="s">
         <v>259</v>
       </c>
-      <c r="D37" s="65" t="s">
+      <c r="D37" s="64" t="s">
         <v>260</v>
       </c>
-      <c r="E37" s="65" t="s">
+      <c r="E37" s="64" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="96"/>
-      <c r="B38" s="96"/>
-      <c r="C38" s="96"/>
-      <c r="D38" s="96"/>
-      <c r="E38" s="96"/>
+      <c r="A38" s="101"/>
+      <c r="B38" s="101"/>
+      <c r="C38" s="101"/>
+      <c r="D38" s="101"/>
+      <c r="E38" s="101"/>
     </row>
     <row r="39" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="86" t="s">
+      <c r="A39" s="85" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="63" t="s">
+      <c r="A40" s="62" t="s">
         <v>262</v>
       </c>
-      <c r="B40" s="105" t="s">
+      <c r="B40" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
+      <c r="C40" s="119"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="119"/>
     </row>
     <row r="41" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="64" t="s">
+      <c r="A41" s="63" t="s">
         <v>264</v>
       </c>
-      <c r="B41" s="97" t="s">
+      <c r="B41" s="105" t="s">
         <v>265</v>
       </c>
-      <c r="C41" s="108"/>
-      <c r="D41" s="108"/>
-      <c r="E41" s="98"/>
+      <c r="C41" s="112"/>
+      <c r="D41" s="112"/>
+      <c r="E41" s="106"/>
     </row>
     <row r="42" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="64" t="s">
+      <c r="A42" s="63" t="s">
         <v>266</v>
       </c>
-      <c r="B42" s="97" t="s">
+      <c r="B42" s="105" t="s">
         <v>267</v>
       </c>
-      <c r="C42" s="108"/>
-      <c r="D42" s="108"/>
-      <c r="E42" s="98"/>
+      <c r="C42" s="112"/>
+      <c r="D42" s="112"/>
+      <c r="E42" s="106"/>
     </row>
     <row r="43" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="64" t="s">
+      <c r="A43" s="63" t="s">
         <v>268</v>
       </c>
-      <c r="B43" s="97" t="s">
+      <c r="B43" s="105" t="s">
         <v>269</v>
       </c>
-      <c r="C43" s="108"/>
-      <c r="D43" s="108"/>
-      <c r="E43" s="98"/>
+      <c r="C43" s="112"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="106"/>
     </row>
     <row r="44" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="64" t="s">
+      <c r="A44" s="63" t="s">
         <v>270</v>
       </c>
-      <c r="B44" s="97" t="s">
+      <c r="B44" s="105" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="108"/>
-      <c r="D44" s="108"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="112"/>
+      <c r="D44" s="112"/>
+      <c r="E44" s="106"/>
     </row>
     <row r="45" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="64" t="s">
+      <c r="A45" s="63" t="s">
         <v>272</v>
       </c>
-      <c r="B45" s="97" t="s">
+      <c r="B45" s="105" t="s">
         <v>273</v>
       </c>
-      <c r="C45" s="108"/>
-      <c r="D45" s="108"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="112"/>
+      <c r="D45" s="112"/>
+      <c r="E45" s="106"/>
     </row>
     <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="64" t="s">
+      <c r="A46" s="63" t="s">
         <v>274</v>
       </c>
-      <c r="B46" s="76" t="s">
+      <c r="B46" s="75" t="s">
         <v>275</v>
       </c>
-      <c r="C46" s="83"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="80"/>
+      <c r="C46" s="82"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="79"/>
     </row>
     <row r="47" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="96"/>
-      <c r="B47" s="96"/>
-      <c r="C47" s="96"/>
-      <c r="D47" s="96"/>
-      <c r="E47" s="96"/>
+      <c r="A47" s="101"/>
+      <c r="B47" s="101"/>
+      <c r="C47" s="101"/>
+      <c r="D47" s="101"/>
+      <c r="E47" s="101"/>
     </row>
     <row r="48" spans="1:5" ht="86.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="85" t="s">
+      <c r="A48" s="84" t="s">
         <v>276</v>
       </c>
     </row>
@@ -10060,256 +10064,256 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="120" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
     </row>
     <row r="2" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
     </row>
     <row r="4" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="52" t="s">
         <v>279</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="52" t="s">
         <v>280</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="52" t="s">
         <v>281</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="52" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="112" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="53" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="112" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="53" t="s">
         <v>287</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="53" t="s">
         <v>288</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="53" t="s">
         <v>289</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="53" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="112" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="53" t="s">
         <v>291</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="53" t="s">
         <v>292</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="53" t="s">
         <v>293</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="53" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="116" t="s">
+      <c r="A8" s="121" t="s">
         <v>295</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
     </row>
     <row r="9" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="107" t="s">
+      <c r="A9" s="111" t="s">
         <v>296</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
     </row>
     <row r="10" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="107" t="s">
+      <c r="A10" s="111" t="s">
         <v>297</v>
       </c>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
     </row>
     <row r="11" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="107" t="s">
+      <c r="A11" s="111" t="s">
         <v>298</v>
       </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="101"/>
     </row>
     <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="116" t="s">
+      <c r="A13" s="121" t="s">
         <v>299</v>
       </c>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="101"/>
     </row>
     <row r="14" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="52" t="s">
         <v>300</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="52" t="s">
         <v>301</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="52" t="s">
         <v>302</v>
       </c>
-      <c r="D14" s="53" t="s">
+      <c r="D14" s="52" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="53" t="s">
         <v>304</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="53" t="s">
         <v>305</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="53" t="s">
         <v>306</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="D15" s="53" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="53" t="s">
         <v>308</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="53" t="s">
         <v>309</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="53" t="s">
         <v>310</v>
       </c>
-      <c r="D16" s="54" t="s">
+      <c r="D16" s="53" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="53" t="s">
         <v>312</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="53" t="s">
         <v>313</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="53" t="s">
         <v>314</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="53" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="53" t="s">
         <v>316</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="53" t="s">
         <v>317</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="53" t="s">
         <v>318</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="53" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="53" t="s">
         <v>320</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="53" t="s">
         <v>321</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="53" t="s">
         <v>318</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="53" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="116" t="s">
+      <c r="A21" s="121" t="s">
         <v>323</v>
       </c>
-      <c r="B21" s="96"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="96"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="101"/>
     </row>
     <row r="22" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="99" t="s">
+      <c r="A22" s="109" t="s">
         <v>324</v>
       </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="96"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="101"/>
     </row>
     <row r="23" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="99" t="s">
+      <c r="A23" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="B23" s="96"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="101"/>
     </row>
     <row r="24" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="99" t="s">
+      <c r="A24" s="109" t="s">
         <v>326</v>
       </c>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
     </row>
     <row r="25" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="99" t="s">
+      <c r="A25" s="109" t="s">
         <v>327</v>
       </c>
-      <c r="B25" s="96"/>
-      <c r="C25" s="96"/>
-      <c r="D25" s="96"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="101"/>
     </row>
     <row r="26" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="99" t="s">
+      <c r="A26" s="109" t="s">
         <v>328</v>
       </c>
-      <c r="B26" s="96"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
     </row>
     <row r="27" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="99" t="s">
+      <c r="A27" s="109" t="s">
         <v>329</v>
       </c>
-      <c r="B27" s="96"/>
-      <c r="C27" s="96"/>
-      <c r="D27" s="96"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -10416,382 +10420,382 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="120" t="s">
         <v>346</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
     </row>
     <row r="2" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="111" t="s">
         <v>347</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
     </row>
     <row r="4" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="52" t="s">
         <v>348</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="52" t="s">
         <v>349</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="52" t="s">
         <v>350</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="52" t="s">
         <v>351</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="52" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="53" t="s">
         <v>353</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="53" t="s">
         <v>354</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="53" t="s">
         <v>355</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="53" t="s">
         <v>356</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="53" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="53" t="s">
         <v>353</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="53" t="s">
         <v>358</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="53" t="s">
         <v>359</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="53" t="s">
         <v>360</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="53" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="53" t="s">
         <v>353</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="53" t="s">
         <v>362</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="53" t="s">
         <v>363</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="53" t="s">
         <v>364</v>
       </c>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="53" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>366</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="53" t="s">
         <v>367</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="53" t="s">
         <v>368</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="53" t="s">
         <v>369</v>
       </c>
-      <c r="E8" s="54" t="s">
+      <c r="E8" s="53" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="53" t="s">
         <v>371</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="53" t="s">
         <v>372</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="53" t="s">
         <v>373</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="53" t="s">
         <v>374</v>
       </c>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="53" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="53" t="s">
         <v>371</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="53" t="s">
         <v>376</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="53" t="s">
         <v>377</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="53" t="s">
         <v>378</v>
       </c>
-      <c r="E10" s="54" t="s">
+      <c r="E10" s="53" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="53" t="s">
         <v>380</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="53" t="s">
         <v>381</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="53" t="s">
         <v>382</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="D11" s="53" t="s">
         <v>383</v>
       </c>
-      <c r="E11" s="54" t="s">
+      <c r="E11" s="53" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="53" t="s">
         <v>385</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="53" t="s">
         <v>386</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="53" t="s">
         <v>387</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="53" t="s">
         <v>388</v>
       </c>
-      <c r="E12" s="54" t="s">
+      <c r="E12" s="53" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="116" t="s">
+      <c r="A14" s="121" t="s">
         <v>390</v>
       </c>
-      <c r="B14" s="96"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
     </row>
     <row r="15" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="52" t="s">
         <v>391</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="52" t="s">
         <v>392</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="52" t="s">
         <v>393</v>
       </c>
-      <c r="D15" s="53" t="s">
+      <c r="D15" s="52" t="s">
         <v>394</v>
       </c>
-      <c r="E15" s="53" t="s">
+      <c r="E15" s="52" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="53" t="s">
         <v>396</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="53" t="s">
         <v>397</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="53" t="s">
         <v>398</v>
       </c>
-      <c r="D16" s="54" t="s">
+      <c r="D16" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="E16" s="54" t="s">
+      <c r="E16" s="53" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="53" t="s">
         <v>401</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="53" t="s">
         <v>402</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="53" t="s">
         <v>403</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="E17" s="54" t="s">
+      <c r="E17" s="53" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="55" t="s">
         <v>405</v>
       </c>
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="55" t="s">
         <v>406</v>
       </c>
-      <c r="C18" s="56" t="s">
+      <c r="C18" s="55" t="s">
         <v>407</v>
       </c>
-      <c r="D18" s="56" t="s">
+      <c r="D18" s="55" t="s">
         <v>408</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="55" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="56" t="s">
         <v>409</v>
       </c>
-      <c r="B19" s="57" t="s">
+      <c r="B19" s="56" t="s">
         <v>410</v>
       </c>
-      <c r="C19" s="57" t="s">
+      <c r="C19" s="56" t="s">
         <v>411</v>
       </c>
-      <c r="D19" s="57" t="s">
+      <c r="D19" s="56" t="s">
         <v>412</v>
       </c>
-      <c r="E19" s="57" t="s">
+      <c r="E19" s="56" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="56" t="s">
         <v>414</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="56" t="s">
         <v>415</v>
       </c>
-      <c r="C20" s="57" t="s">
+      <c r="C20" s="56" t="s">
         <v>416</v>
       </c>
-      <c r="D20" s="57" t="s">
+      <c r="D20" s="56" t="s">
         <v>417</v>
       </c>
-      <c r="E20" s="57" t="s">
+      <c r="E20" s="56" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="56" t="s">
         <v>419</v>
       </c>
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="56" t="s">
         <v>420</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="56" t="s">
         <v>421</v>
       </c>
-      <c r="D21" s="57" t="s">
+      <c r="D21" s="56" t="s">
         <v>422</v>
       </c>
-      <c r="E21" s="57" t="s">
+      <c r="E21" s="56" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="56" t="s">
         <v>424</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="56" t="s">
         <v>425</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="C22" s="56" t="s">
         <v>426</v>
       </c>
-      <c r="D22" s="57" t="s">
+      <c r="D22" s="56" t="s">
         <v>422</v>
       </c>
-      <c r="E22" s="57" t="s">
+      <c r="E22" s="56" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="53" t="s">
         <v>428</v>
       </c>
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="53" t="s">
         <v>429</v>
       </c>
-      <c r="C23" s="54" t="s">
+      <c r="C23" s="53" t="s">
         <v>430</v>
       </c>
-      <c r="D23" s="54" t="s">
+      <c r="D23" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="E23" s="54" t="s">
+      <c r="E23" s="53" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="117" t="s">
+      <c r="A25" s="122" t="s">
         <v>432</v>
       </c>
-      <c r="B25" s="96"/>
-      <c r="C25" s="96"/>
-      <c r="D25" s="96"/>
-      <c r="E25" s="96"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
     </row>
     <row r="26" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="107" t="s">
+      <c r="A26" s="111" t="s">
         <v>433</v>
       </c>
-      <c r="B26" s="96"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="101"/>
     </row>
     <row r="27" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="107" t="s">
+      <c r="A27" s="111" t="s">
         <v>434</v>
       </c>
-      <c r="B27" s="96"/>
-      <c r="C27" s="96"/>
-      <c r="D27" s="96"/>
-      <c r="E27" s="96"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="101"/>
     </row>
     <row r="28" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="107" t="s">
+      <c r="A28" s="111" t="s">
         <v>435</v>
       </c>
-      <c r="B28" s="96"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="96"/>
-      <c r="E28" s="96"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
     </row>
     <row r="29" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="107" t="s">
+      <c r="A29" s="111" t="s">
         <v>436</v>
       </c>
-      <c r="B29" s="96"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="96"/>
-      <c r="E29" s="96"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="101"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -10820,7 +10824,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.3" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="58" t="s">
         <v>437</v>
       </c>
       <c r="B1" s="9"/>
@@ -10828,7 +10832,7 @@
       <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="59" t="s">
         <v>438</v>
       </c>
       <c r="B2" s="9"/>
@@ -11251,7 +11255,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="39" t="s">
         <v>514</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -11291,7 +11295,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="39" t="s">
         <v>524</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -11325,7 +11329,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="39" t="s">
         <v>530</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -11359,7 +11363,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="39" t="s">
         <v>536</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -11395,7 +11399,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="39" t="s">
         <v>543</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -11535,7 +11539,7 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="39" t="s">
         <v>570</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -11963,13 +11967,13 @@
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="44" t="s">
         <v>654</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="40" t="s">
         <v>646</v>
       </c>
-      <c r="D22" s="42" t="s">
+      <c r="D22" s="41" t="s">
         <v>454</v>
       </c>
       <c r="E22" s="16" t="s">
@@ -11999,13 +12003,13 @@
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="40" t="s">
         <v>646</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="41" t="s">
         <v>457</v>
       </c>
       <c r="E23" s="16" t="s">
@@ -12037,13 +12041,13 @@
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="45" t="s">
         <v>668</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="42" t="s">
         <v>646</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="43" t="s">
         <v>454</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -12073,13 +12077,13 @@
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="42" t="s">
         <v>646</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="43" t="s">
         <v>457</v>
       </c>
       <c r="E25" s="16" t="s">
@@ -12109,13 +12113,13 @@
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="44" t="s">
         <v>681</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="40" t="s">
         <v>646</v>
       </c>
-      <c r="D26" s="42" t="s">
+      <c r="D26" s="41" t="s">
         <v>454</v>
       </c>
       <c r="E26" s="16" t="s">
@@ -12143,13 +12147,13 @@
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="40" t="s">
         <v>646</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="41" t="s">
         <v>451</v>
       </c>
       <c r="E27" s="16" t="s">
@@ -12187,13 +12191,13 @@
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="40" t="s">
         <v>646</v>
       </c>
-      <c r="D28" s="42" t="s">
+      <c r="D28" s="41" t="s">
         <v>457</v>
       </c>
       <c r="E28" s="16" t="s">
@@ -12225,13 +12229,13 @@
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="D29" s="42" t="s">
+      <c r="D29" s="41" t="s">
         <v>451</v>
       </c>
       <c r="E29" s="16" t="s">
@@ -12269,13 +12273,13 @@
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="D30" s="42" t="s">
+      <c r="D30" s="41" t="s">
         <v>448</v>
       </c>
       <c r="E30" s="16" t="s">
@@ -12311,13 +12315,13 @@
       <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="D31" s="42" t="s">
+      <c r="D31" s="41" t="s">
         <v>454</v>
       </c>
       <c r="E31" s="16" t="s">
@@ -12353,13 +12357,13 @@
       <c r="A32" s="2">
         <v>30</v>
       </c>
-      <c r="B32" s="94" t="s">
+      <c r="B32" s="91" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="41" t="s">
         <v>703</v>
       </c>
-      <c r="D32" s="42" t="s">
+      <c r="D32" s="41" t="s">
         <v>454</v>
       </c>
       <c r="E32" s="16" t="s">
@@ -12395,13 +12399,13 @@
       <c r="A33" s="2">
         <v>31</v>
       </c>
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="D33" s="42" t="s">
+      <c r="D33" s="41" t="s">
         <v>448</v>
       </c>
       <c r="E33" s="16" t="s">
@@ -12439,13 +12443,13 @@
       <c r="A34" s="2">
         <v>32</v>
       </c>
-      <c r="B34" s="45" t="s">
+      <c r="B34" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="D34" s="42" t="s">
+      <c r="D34" s="41" t="s">
         <v>454</v>
       </c>
       <c r="E34" s="16" t="s">
@@ -12483,13 +12487,13 @@
       <c r="A35" s="2">
         <v>33</v>
       </c>
-      <c r="B35" s="45" t="s">
+      <c r="B35" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="C35" s="41" t="s">
+      <c r="C35" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="D35" s="42" t="s">
+      <c r="D35" s="41" t="s">
         <v>454</v>
       </c>
       <c r="E35" s="16" t="s">
@@ -12527,13 +12531,13 @@
       <c r="A36" s="2">
         <v>34</v>
       </c>
-      <c r="B36" s="45" t="s">
+      <c r="B36" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="C36" s="41" t="s">
+      <c r="C36" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="D36" s="42" t="s">
+      <c r="D36" s="41" t="s">
         <v>457</v>
       </c>
       <c r="E36" s="16" t="s">
@@ -12569,13 +12573,13 @@
       <c r="A37" s="2">
         <v>35</v>
       </c>
-      <c r="B37" s="45" t="s">
+      <c r="B37" s="44" t="s">
         <v>218</v>
       </c>
-      <c r="C37" s="41" t="s">
+      <c r="C37" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="D37" s="42" t="s">
+      <c r="D37" s="41" t="s">
         <v>461</v>
       </c>
       <c r="E37" s="16" t="s">
@@ -12605,13 +12609,13 @@
       <c r="A38" s="2">
         <v>36</v>
       </c>
-      <c r="B38" s="45" t="s">
+      <c r="B38" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="C38" s="41" t="s">
+      <c r="C38" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="D38" s="42" t="s">
+      <c r="D38" s="41" t="s">
         <v>457</v>
       </c>
       <c r="E38" s="16" t="s">
@@ -12649,7 +12653,7 @@
       <c r="A39" s="29">
         <v>37</v>
       </c>
-      <c r="B39" s="90" t="s">
+      <c r="B39" s="87" t="s">
         <v>155</v>
       </c>
       <c r="C39" s="35" t="s">
@@ -12681,11 +12685,11 @@
       <c r="M39" s="31"/>
       <c r="N39" s="31"/>
     </row>
-    <row r="40" spans="1:14" s="88" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="118">
+    <row r="40" spans="1:14" s="33" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="29">
         <v>38</v>
       </c>
-      <c r="B40" s="122" t="s">
+      <c r="B40" s="87" t="s">
         <v>794</v>
       </c>
       <c r="C40" s="123" t="s">
@@ -12694,34 +12698,34 @@
       <c r="D40" s="124" t="s">
         <v>454</v>
       </c>
-      <c r="E40" s="87" t="s">
+      <c r="E40" s="32" t="s">
         <v>795</v>
       </c>
-      <c r="F40" s="87" t="s">
+      <c r="F40" s="32" t="s">
         <v>796</v>
       </c>
-      <c r="G40" s="87" t="s">
+      <c r="G40" s="32" t="s">
         <v>683</v>
       </c>
-      <c r="H40" s="87" t="s">
+      <c r="H40" s="32" t="s">
         <v>672</v>
       </c>
-      <c r="I40" s="87" t="s">
+      <c r="I40" s="32" t="s">
         <v>797</v>
       </c>
-      <c r="J40" s="87" t="s">
+      <c r="J40" s="32" t="s">
         <v>798</v>
       </c>
-      <c r="K40" s="39"/>
-      <c r="L40" s="39"/>
-      <c r="M40" s="39"/>
-      <c r="N40" s="39"/>
-    </row>
-    <row r="41" spans="1:14" s="88" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="118">
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+    </row>
+    <row r="41" spans="1:14" s="33" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="29">
         <v>39</v>
       </c>
-      <c r="B41" s="122" t="s">
+      <c r="B41" s="87" t="s">
         <v>799</v>
       </c>
       <c r="C41" s="123" t="s">
@@ -12730,28 +12734,28 @@
       <c r="D41" s="124" t="s">
         <v>461</v>
       </c>
-      <c r="E41" s="87" t="s">
+      <c r="E41" s="32" t="s">
         <v>800</v>
       </c>
-      <c r="F41" s="87" t="s">
+      <c r="F41" s="32" t="s">
         <v>801</v>
       </c>
-      <c r="G41" s="87" t="s">
+      <c r="G41" s="32" t="s">
         <v>802</v>
       </c>
-      <c r="H41" s="87" t="s">
+      <c r="H41" s="32" t="s">
         <v>803</v>
       </c>
-      <c r="I41" s="87" t="s">
+      <c r="I41" s="32" t="s">
         <v>804</v>
       </c>
-      <c r="J41" s="87" t="s">
+      <c r="J41" s="32" t="s">
         <v>805</v>
       </c>
-      <c r="K41" s="39"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
     </row>
     <row r="42" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2">
@@ -12760,10 +12764,10 @@
       <c r="B42" s="38" t="s">
         <v>806</v>
       </c>
-      <c r="C42" s="43" t="s">
+      <c r="C42" s="42" t="s">
         <v>646</v>
       </c>
-      <c r="D42" s="44" t="s">
+      <c r="D42" s="43" t="s">
         <v>457</v>
       </c>
       <c r="E42" s="16" t="s">
@@ -12796,10 +12800,10 @@
       <c r="B43" s="38" t="s">
         <v>813</v>
       </c>
-      <c r="C43" s="43" t="s">
+      <c r="C43" s="42" t="s">
         <v>646</v>
       </c>
-      <c r="D43" s="44" t="s">
+      <c r="D43" s="43" t="s">
         <v>461</v>
       </c>
       <c r="E43" s="16" t="s">
@@ -12830,10 +12834,10 @@
       <c r="B44" s="38" t="s">
         <v>818</v>
       </c>
-      <c r="C44" s="41" t="s">
+      <c r="C44" s="40" t="s">
         <v>646</v>
       </c>
-      <c r="D44" s="42" t="s">
+      <c r="D44" s="41" t="s">
         <v>454</v>
       </c>
       <c r="E44" s="16" t="s">
@@ -12864,10 +12868,10 @@
       <c r="B45" s="38" t="s">
         <v>823</v>
       </c>
-      <c r="C45" s="41" t="s">
+      <c r="C45" s="40" t="s">
         <v>646</v>
       </c>
-      <c r="D45" s="42" t="s">
+      <c r="D45" s="41" t="s">
         <v>457</v>
       </c>
       <c r="E45" s="16" t="s">
@@ -15755,7 +15759,7 @@
       <c r="B26" s="34" t="s">
         <v>681</v>
       </c>
-      <c r="C26" s="89" t="s">
+      <c r="C26" s="86" t="s">
         <v>646</v>
       </c>
       <c r="D26" s="31" t="s">
@@ -15805,7 +15809,7 @@
       <c r="B27" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="89" t="s">
+      <c r="C27" s="86" t="s">
         <v>646</v>
       </c>
       <c r="D27" s="31" t="s">
@@ -15861,7 +15865,7 @@
       <c r="B28" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="86" t="s">
         <v>646</v>
       </c>
       <c r="D28" s="31" t="s">
@@ -15914,16 +15918,16 @@
       <c r="A29" s="29">
         <v>28</v>
       </c>
-      <c r="B29" s="90" t="s">
+      <c r="B29" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="89" t="s">
+      <c r="C29" s="86" t="s">
         <v>703</v>
       </c>
-      <c r="D29" s="93" t="s">
+      <c r="D29" s="90" t="s">
         <v>451</v>
       </c>
-      <c r="E29" s="91" t="s">
+      <c r="E29" s="88" t="s">
         <v>1207</v>
       </c>
       <c r="F29" s="32" t="s">
@@ -15973,7 +15977,7 @@
       <c r="B30" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="89" t="s">
+      <c r="C30" s="86" t="s">
         <v>703</v>
       </c>
       <c r="D30" s="31" t="s">
@@ -16029,7 +16033,7 @@
       <c r="B31" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="89" t="s">
+      <c r="C31" s="86" t="s">
         <v>703</v>
       </c>
       <c r="D31" s="31" t="s">
@@ -16085,7 +16089,7 @@
       <c r="B32" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="93" t="s">
+      <c r="C32" s="90" t="s">
         <v>703</v>
       </c>
       <c r="D32" s="31" t="s">
@@ -16141,13 +16145,13 @@
       <c r="B33" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="C33" s="89" t="s">
+      <c r="C33" s="86" t="s">
         <v>703</v>
       </c>
       <c r="D33" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="E33" s="91" t="s">
+      <c r="E33" s="88" t="s">
         <v>1226</v>
       </c>
       <c r="F33" s="32" t="s">
@@ -16197,7 +16201,7 @@
       <c r="B34" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="86" t="s">
         <v>703</v>
       </c>
       <c r="D34" s="31" t="s">
@@ -16253,7 +16257,7 @@
       <c r="B35" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="C35" s="89" t="s">
+      <c r="C35" s="86" t="s">
         <v>703</v>
       </c>
       <c r="D35" s="31" t="s">
@@ -16309,7 +16313,7 @@
       <c r="B36" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="C36" s="89" t="s">
+      <c r="C36" s="86" t="s">
         <v>703</v>
       </c>
       <c r="D36" s="31" t="s">
@@ -16362,10 +16366,10 @@
       <c r="A37" s="29">
         <v>35</v>
       </c>
-      <c r="B37" s="90" t="s">
+      <c r="B37" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="C37" s="89" t="s">
+      <c r="C37" s="86" t="s">
         <v>703</v>
       </c>
       <c r="D37" s="31" t="s">
@@ -16421,13 +16425,13 @@
       <c r="B38" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="C38" s="89" t="s">
+      <c r="C38" s="86" t="s">
         <v>703</v>
       </c>
       <c r="D38" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="E38" s="91" t="s">
+      <c r="E38" s="88" t="s">
         <v>153</v>
       </c>
       <c r="F38" s="32" t="s">
@@ -16580,7 +16584,7 @@
       <c r="A41" s="29">
         <v>39</v>
       </c>
-      <c r="B41" s="90" t="s">
+      <c r="B41" s="87" t="s">
         <v>799</v>
       </c>
       <c r="C41" s="35" t="s">
@@ -16624,51 +16628,51 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="88" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="118">
+    <row r="42" spans="1:18" s="33" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="29">
         <v>40</v>
       </c>
-      <c r="B42" s="120" t="s">
+      <c r="B42" s="34" t="s">
         <v>806</v>
       </c>
-      <c r="C42" s="121" t="s">
+      <c r="C42" s="35" t="s">
         <v>646</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="E42" s="119"/>
-      <c r="F42" s="87" t="s">
+      <c r="E42" s="30"/>
+      <c r="F42" s="32" t="s">
         <v>1268</v>
       </c>
-      <c r="G42" s="87" t="s">
+      <c r="G42" s="32" t="s">
         <v>1114</v>
       </c>
-      <c r="H42" s="87"/>
-      <c r="I42" s="87" t="s">
+      <c r="H42" s="32"/>
+      <c r="I42" s="32" t="s">
         <v>1269</v>
       </c>
-      <c r="J42" s="87" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K42" s="87" t="s">
-        <v>1613</v>
-      </c>
-      <c r="L42" s="39"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="87" t="s">
+      <c r="J42" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K42" s="32" t="s">
+        <v>1612</v>
+      </c>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="32" t="s">
         <v>1075</v>
       </c>
-      <c r="O42" s="87" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P42" s="87" t="s">
+      <c r="O42" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P42" s="32" t="s">
         <v>1270</v>
       </c>
-      <c r="Q42" s="87" t="s">
+      <c r="Q42" s="32" t="s">
         <v>1271</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="32" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -16676,7 +16680,7 @@
       <c r="A43" s="29">
         <v>41</v>
       </c>
-      <c r="B43" s="90" t="s">
+      <c r="B43" s="87" t="s">
         <v>813</v>
       </c>
       <c r="C43" s="35" t="s">
@@ -16765,7 +16769,7 @@
         <v>1171</v>
       </c>
       <c r="R44" s="32" t="s">
-        <v>1276</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="45" spans="1:18" s="33" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -16783,20 +16787,20 @@
       </c>
       <c r="E45" s="30"/>
       <c r="F45" s="32" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="G45" s="32" t="s">
         <v>1114</v>
       </c>
       <c r="H45" s="32"/>
       <c r="I45" s="32" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J45" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K45" s="32" t="s">
         <v>1278</v>
-      </c>
-      <c r="J45" s="32" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K45" s="32" t="s">
-        <v>1279</v>
       </c>
       <c r="L45" s="31"/>
       <c r="M45" s="31"/>
@@ -16807,13 +16811,13 @@
         <v>1071</v>
       </c>
       <c r="P45" s="32" t="s">
+        <v>1279</v>
+      </c>
+      <c r="Q45" s="32" t="s">
         <v>1280</v>
       </c>
-      <c r="Q45" s="32" t="s">
+      <c r="R45" s="32" t="s">
         <v>1281</v>
-      </c>
-      <c r="R45" s="32" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="46" spans="1:18" s="33" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -16830,13 +16834,13 @@
         <v>448</v>
       </c>
       <c r="E46" s="32" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F46" s="32" t="s">
         <v>1283</v>
       </c>
-      <c r="F46" s="32" t="s">
+      <c r="G46" s="32" t="s">
         <v>1284</v>
-      </c>
-      <c r="G46" s="32" t="s">
-        <v>1285</v>
       </c>
       <c r="H46" s="32" t="s">
         <v>1079</v>
@@ -16848,10 +16852,10 @@
         <v>1080</v>
       </c>
       <c r="K46" s="32" t="s">
+        <v>1285</v>
+      </c>
+      <c r="L46" s="32" t="s">
         <v>1286</v>
-      </c>
-      <c r="L46" s="32" t="s">
-        <v>1287</v>
       </c>
       <c r="M46" s="32" t="s">
         <v>1074</v>
@@ -16866,13 +16870,13 @@
         <v>1071</v>
       </c>
       <c r="Q46" s="32" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="R46" s="32" t="s">
         <v>1071</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:18" s="33" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="29">
         <v>45</v>
       </c>
@@ -16887,10 +16891,10 @@
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="32" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G47" s="32" t="s">
         <v>1289</v>
-      </c>
-      <c r="G47" s="32" t="s">
-        <v>1290</v>
       </c>
       <c r="H47" s="32" t="s">
         <v>1079</v>
@@ -16902,7 +16906,7 @@
         <v>1080</v>
       </c>
       <c r="K47" s="32" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="L47" s="31"/>
       <c r="M47" s="31"/>
@@ -16919,551 +16923,551 @@
         <v>1171</v>
       </c>
       <c r="R47" s="32" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" s="33" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="29">
+        <v>46</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>843</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>646</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>457</v>
+      </c>
+      <c r="E48" s="30"/>
+      <c r="F48" s="32" t="s">
         <v>1292</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="2">
-        <v>46</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>843</v>
-      </c>
-      <c r="C48" s="15" t="s">
+      <c r="G48" s="32" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32" t="s">
+        <v>1293</v>
+      </c>
+      <c r="J48" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K48" s="32" t="s">
+        <v>1294</v>
+      </c>
+      <c r="L48" s="31"/>
+      <c r="M48" s="31"/>
+      <c r="N48" s="32" t="s">
+        <v>1075</v>
+      </c>
+      <c r="O48" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P48" s="32" t="s">
+        <v>1295</v>
+      </c>
+      <c r="Q48" s="32" t="s">
+        <v>1296</v>
+      </c>
+      <c r="R48" s="32" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" s="33" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="29">
+        <v>47</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>850</v>
+      </c>
+      <c r="C49" s="35" t="s">
         <v>646</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D49" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="E49" s="32" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G49" s="32" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H49" s="32" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I49" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J49" s="32" t="s">
+        <v>1080</v>
+      </c>
+      <c r="K49" s="32" t="s">
+        <v>1300</v>
+      </c>
+      <c r="L49" s="32" t="s">
+        <v>1301</v>
+      </c>
+      <c r="M49" s="32" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N49" s="32" t="s">
+        <v>1075</v>
+      </c>
+      <c r="O49" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P49" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Q49" s="32" t="s">
+        <v>1302</v>
+      </c>
+      <c r="R49" s="32" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" s="33" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="29">
+        <v>48</v>
+      </c>
+      <c r="B50" s="34" t="s">
+        <v>855</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>646</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>454</v>
+      </c>
+      <c r="E50" s="30"/>
+      <c r="F50" s="32" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G50" s="32" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H50" s="32" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I50" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J50" s="32" t="s">
+        <v>1080</v>
+      </c>
+      <c r="K50" s="32" t="s">
+        <v>1305</v>
+      </c>
+      <c r="L50" s="31"/>
+      <c r="M50" s="31"/>
+      <c r="N50" s="32" t="s">
+        <v>1075</v>
+      </c>
+      <c r="O50" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P50" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Q50" s="32" t="s">
+        <v>1171</v>
+      </c>
+      <c r="R50" s="32" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" s="33" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="29">
+        <v>49</v>
+      </c>
+      <c r="B51" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>646</v>
+      </c>
+      <c r="D51" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="16" t="s">
-        <v>1293</v>
-      </c>
-      <c r="G48" s="16" t="s">
+      <c r="E51" s="30"/>
+      <c r="F51" s="32" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G51" s="32" t="s">
         <v>1114</v>
       </c>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16" t="s">
-        <v>1294</v>
-      </c>
-      <c r="J48" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K48" s="16" t="s">
-        <v>1295</v>
-      </c>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="16" t="s">
+      <c r="H51" s="32"/>
+      <c r="I51" s="32" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J51" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K51" s="32" t="s">
+        <v>1309</v>
+      </c>
+      <c r="L51" s="31"/>
+      <c r="M51" s="31"/>
+      <c r="N51" s="32" t="s">
         <v>1075</v>
       </c>
-      <c r="O48" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P48" s="16" t="s">
-        <v>1296</v>
-      </c>
-      <c r="Q48" s="16" t="s">
-        <v>1297</v>
-      </c>
-      <c r="R48" s="16" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="2">
-        <v>47</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>850</v>
-      </c>
-      <c r="C49" s="15" t="s">
+      <c r="O51" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P51" s="32" t="s">
+        <v>1310</v>
+      </c>
+      <c r="Q51" s="32" t="s">
+        <v>1311</v>
+      </c>
+      <c r="R51" s="32" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" s="33" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="29">
+        <v>50</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>863</v>
+      </c>
+      <c r="C52" s="35" t="s">
         <v>646</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>1298</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>1299</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>1300</v>
-      </c>
-      <c r="H49" s="16" t="s">
+      <c r="D52" s="31" t="s">
+        <v>454</v>
+      </c>
+      <c r="E52" s="30"/>
+      <c r="F52" s="32" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G52" s="32" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H52" s="32" t="s">
         <v>1079</v>
       </c>
-      <c r="I49" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="J49" s="16" t="s">
+      <c r="I52" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J52" s="32" t="s">
         <v>1080</v>
       </c>
-      <c r="K49" s="16" t="s">
-        <v>1301</v>
-      </c>
-      <c r="L49" s="16" t="s">
-        <v>1302</v>
-      </c>
-      <c r="M49" s="16" t="s">
-        <v>1074</v>
-      </c>
-      <c r="N49" s="16" t="s">
+      <c r="K52" s="32" t="s">
+        <v>1314</v>
+      </c>
+      <c r="L52" s="31"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="32" t="s">
         <v>1075</v>
       </c>
-      <c r="O49" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P49" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="Q49" s="16" t="s">
-        <v>1303</v>
-      </c>
-      <c r="R49" s="16" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="2">
-        <v>48</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>855</v>
-      </c>
-      <c r="C50" s="15" t="s">
+      <c r="O52" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P52" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Q52" s="32" t="s">
+        <v>1171</v>
+      </c>
+      <c r="R52" s="32" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" s="33" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="29">
+        <v>51</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>866</v>
+      </c>
+      <c r="C53" s="35" t="s">
         <v>646</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D53" s="31" t="s">
+        <v>457</v>
+      </c>
+      <c r="E53" s="30"/>
+      <c r="F53" s="32" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G53" s="32" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32" t="s">
+        <v>1317</v>
+      </c>
+      <c r="J53" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K53" s="32" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L53" s="31"/>
+      <c r="M53" s="31"/>
+      <c r="N53" s="32" t="s">
+        <v>1075</v>
+      </c>
+      <c r="O53" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P53" s="32" t="s">
+        <v>1319</v>
+      </c>
+      <c r="Q53" s="32" t="s">
+        <v>1320</v>
+      </c>
+      <c r="R53" s="32" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" s="33" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="29">
+        <v>52</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>870</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>646</v>
+      </c>
+      <c r="D54" s="31" t="s">
         <v>454</v>
       </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="16" t="s">
-        <v>1304</v>
-      </c>
-      <c r="G50" s="16" t="s">
-        <v>1305</v>
-      </c>
-      <c r="H50" s="16" t="s">
+      <c r="E54" s="30"/>
+      <c r="F54" s="32" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G54" s="32" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H54" s="32" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I54" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J54" s="32" t="s">
+        <v>1080</v>
+      </c>
+      <c r="K54" s="32" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L54" s="31"/>
+      <c r="M54" s="31"/>
+      <c r="N54" s="32" t="s">
+        <v>1075</v>
+      </c>
+      <c r="O54" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P54" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Q54" s="32" t="s">
+        <v>1171</v>
+      </c>
+      <c r="R54" s="32" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" s="33" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="29">
+        <v>53</v>
+      </c>
+      <c r="B55" s="34" t="s">
+        <v>873</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>646</v>
+      </c>
+      <c r="D55" s="31" t="s">
+        <v>457</v>
+      </c>
+      <c r="E55" s="30"/>
+      <c r="F55" s="32" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G55" s="32" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32" t="s">
+        <v>1327</v>
+      </c>
+      <c r="J55" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K55" s="32" t="s">
+        <v>1328</v>
+      </c>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="32" t="s">
+        <v>1075</v>
+      </c>
+      <c r="O55" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P55" s="32" t="s">
+        <v>1329</v>
+      </c>
+      <c r="Q55" s="32" t="s">
+        <v>1330</v>
+      </c>
+      <c r="R55" s="32" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" s="33" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="29">
+        <v>54</v>
+      </c>
+      <c r="B56" s="34" t="s">
+        <v>876</v>
+      </c>
+      <c r="C56" s="35" t="s">
+        <v>646</v>
+      </c>
+      <c r="D56" s="31" t="s">
+        <v>454</v>
+      </c>
+      <c r="E56" s="30"/>
+      <c r="F56" s="32" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G56" s="32" t="s">
+        <v>1332</v>
+      </c>
+      <c r="H56" s="32" t="s">
         <v>1079</v>
       </c>
-      <c r="I50" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="J50" s="16" t="s">
+      <c r="I56" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J56" s="32" t="s">
         <v>1080</v>
       </c>
-      <c r="K50" s="16" t="s">
-        <v>1306</v>
-      </c>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="16" t="s">
+      <c r="K56" s="32" t="s">
+        <v>1333</v>
+      </c>
+      <c r="L56" s="31"/>
+      <c r="M56" s="31"/>
+      <c r="N56" s="32" t="s">
         <v>1075</v>
       </c>
-      <c r="O50" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P50" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="Q50" s="16" t="s">
+      <c r="O56" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P56" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Q56" s="32" t="s">
         <v>1171</v>
       </c>
-      <c r="R50" s="16" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="2">
-        <v>49</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>858</v>
-      </c>
-      <c r="C51" s="15" t="s">
+      <c r="R56" s="32" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" s="33" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="29">
+        <v>55</v>
+      </c>
+      <c r="B57" s="34" t="s">
+        <v>879</v>
+      </c>
+      <c r="C57" s="35" t="s">
         <v>646</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D57" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="16" t="s">
-        <v>1308</v>
-      </c>
-      <c r="G51" s="16" t="s">
+      <c r="E57" s="30"/>
+      <c r="F57" s="32" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G57" s="32" t="s">
         <v>1114</v>
       </c>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16" t="s">
-        <v>1309</v>
-      </c>
-      <c r="J51" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K51" s="16" t="s">
-        <v>1310</v>
-      </c>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="16" t="s">
+      <c r="H57" s="32"/>
+      <c r="I57" s="32" t="s">
+        <v>1336</v>
+      </c>
+      <c r="J57" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K57" s="32" t="s">
+        <v>1337</v>
+      </c>
+      <c r="L57" s="31"/>
+      <c r="M57" s="31"/>
+      <c r="N57" s="32" t="s">
         <v>1075</v>
       </c>
-      <c r="O51" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P51" s="16" t="s">
-        <v>1311</v>
-      </c>
-      <c r="Q51" s="16" t="s">
-        <v>1312</v>
-      </c>
-      <c r="R51" s="16" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="2">
-        <v>50</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>863</v>
-      </c>
-      <c r="C52" s="15" t="s">
+      <c r="O57" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P57" s="32" t="s">
+        <v>1338</v>
+      </c>
+      <c r="Q57" s="32" t="s">
+        <v>1339</v>
+      </c>
+      <c r="R57" s="32" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" s="99" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="93">
+        <v>56</v>
+      </c>
+      <c r="B58" s="94" t="s">
+        <v>883</v>
+      </c>
+      <c r="C58" s="95" t="s">
         <v>646</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D58" s="96" t="s">
         <v>454</v>
       </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="16" t="s">
-        <v>1313</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>1314</v>
-      </c>
-      <c r="H52" s="16" t="s">
-        <v>1079</v>
-      </c>
-      <c r="I52" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="J52" s="16" t="s">
+      <c r="E58" s="97"/>
+      <c r="F58" s="98" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G58" s="98" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H58" s="98"/>
+      <c r="I58" s="98" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J58" s="98" t="s">
         <v>1080</v>
       </c>
-      <c r="K52" s="16" t="s">
-        <v>1315</v>
-      </c>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="16" t="s">
+      <c r="K58" s="98" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L58" s="96"/>
+      <c r="M58" s="96"/>
+      <c r="N58" s="98" t="s">
         <v>1075</v>
       </c>
-      <c r="O52" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P52" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="Q52" s="16" t="s">
+      <c r="O58" s="98" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P58" s="98" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Q58" s="98" t="s">
         <v>1171</v>
       </c>
-      <c r="R52" s="16" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="2">
-        <v>51</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>866</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="16" t="s">
-        <v>1317</v>
-      </c>
-      <c r="G53" s="16" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H53" s="16"/>
-      <c r="I53" s="16" t="s">
-        <v>1318</v>
-      </c>
-      <c r="J53" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K53" s="16" t="s">
-        <v>1319</v>
-      </c>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="16" t="s">
-        <v>1075</v>
-      </c>
-      <c r="O53" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P53" s="16" t="s">
-        <v>1320</v>
-      </c>
-      <c r="Q53" s="16" t="s">
-        <v>1321</v>
-      </c>
-      <c r="R53" s="16" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="2">
-        <v>52</v>
-      </c>
-      <c r="B54" s="14" t="s">
-        <v>870</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="16" t="s">
-        <v>1322</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>1323</v>
-      </c>
-      <c r="H54" s="16" t="s">
-        <v>1324</v>
-      </c>
-      <c r="I54" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="J54" s="16" t="s">
-        <v>1080</v>
-      </c>
-      <c r="K54" s="16" t="s">
-        <v>1325</v>
-      </c>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="16" t="s">
-        <v>1075</v>
-      </c>
-      <c r="O54" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P54" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="Q54" s="16" t="s">
-        <v>1171</v>
-      </c>
-      <c r="R54" s="16" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="2">
-        <v>53</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>873</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="16" t="s">
-        <v>1327</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16" t="s">
-        <v>1328</v>
-      </c>
-      <c r="J55" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K55" s="16" t="s">
-        <v>1329</v>
-      </c>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="16" t="s">
-        <v>1075</v>
-      </c>
-      <c r="O55" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P55" s="16" t="s">
-        <v>1330</v>
-      </c>
-      <c r="Q55" s="16" t="s">
-        <v>1331</v>
-      </c>
-      <c r="R55" s="16" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="2">
-        <v>54</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>876</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="16" t="s">
-        <v>1332</v>
-      </c>
-      <c r="G56" s="16" t="s">
-        <v>1333</v>
-      </c>
-      <c r="H56" s="16" t="s">
-        <v>1079</v>
-      </c>
-      <c r="I56" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="J56" s="16" t="s">
-        <v>1080</v>
-      </c>
-      <c r="K56" s="16" t="s">
-        <v>1334</v>
-      </c>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="16" t="s">
-        <v>1075</v>
-      </c>
-      <c r="O56" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P56" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="Q56" s="16" t="s">
-        <v>1171</v>
-      </c>
-      <c r="R56" s="16" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="2">
-        <v>55</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>879</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="16" t="s">
-        <v>1336</v>
-      </c>
-      <c r="G57" s="16" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16" t="s">
-        <v>1337</v>
-      </c>
-      <c r="J57" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K57" s="16" t="s">
-        <v>1338</v>
-      </c>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="16" t="s">
-        <v>1075</v>
-      </c>
-      <c r="O57" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P57" s="16" t="s">
-        <v>1339</v>
-      </c>
-      <c r="Q57" s="16" t="s">
-        <v>1340</v>
-      </c>
-      <c r="R57" s="16" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="2">
-        <v>56</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>883</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="16" t="s">
-        <v>1341</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>1342</v>
-      </c>
-      <c r="H58" s="16"/>
-      <c r="I58" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="J58" s="16" t="s">
-        <v>1080</v>
-      </c>
-      <c r="K58" s="16" t="s">
+      <c r="R58" s="98" t="s">
         <v>1343</v>
-      </c>
-      <c r="L58" s="3"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="16" t="s">
-        <v>1075</v>
-      </c>
-      <c r="O58" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P58" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="Q58" s="16" t="s">
-        <v>1171</v>
-      </c>
-      <c r="R58" s="16" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -17476,25 +17480,25 @@
       <c r="C59" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="92" t="s">
         <v>457</v>
       </c>
       <c r="E59" s="13"/>
       <c r="F59" s="16" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>1114</v>
       </c>
       <c r="H59" s="16"/>
       <c r="I59" s="16" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J59" s="16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K59" s="16" t="s">
         <v>1346</v>
-      </c>
-      <c r="J59" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K59" s="16" t="s">
-        <v>1347</v>
       </c>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
@@ -17505,10 +17509,10 @@
         <v>1071</v>
       </c>
       <c r="P59" s="16" t="s">
+        <v>1347</v>
+      </c>
+      <c r="Q59" s="16" t="s">
         <v>1348</v>
-      </c>
-      <c r="Q59" s="16" t="s">
-        <v>1349</v>
       </c>
       <c r="R59" s="16" t="s">
         <v>1071</v>
@@ -17529,10 +17533,10 @@
       </c>
       <c r="E60" s="13"/>
       <c r="F60" s="16" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G60" s="16" t="s">
         <v>1350</v>
-      </c>
-      <c r="G60" s="16" t="s">
-        <v>1351</v>
       </c>
       <c r="H60" s="16" t="s">
         <v>1079</v>
@@ -17544,7 +17548,7 @@
         <v>1080</v>
       </c>
       <c r="K60" s="16" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
@@ -17561,7 +17565,7 @@
         <v>1171</v>
       </c>
       <c r="R60" s="16" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -17574,25 +17578,25 @@
       <c r="C61" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="92" t="s">
         <v>457</v>
       </c>
       <c r="E61" s="13"/>
       <c r="F61" s="16" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>1114</v>
       </c>
       <c r="H61" s="16"/>
       <c r="I61" s="16" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J61" s="16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K61" s="16" t="s">
         <v>1355</v>
-      </c>
-      <c r="J61" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K61" s="16" t="s">
-        <v>1356</v>
       </c>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
@@ -17603,10 +17607,10 @@
         <v>1071</v>
       </c>
       <c r="P61" s="16" t="s">
+        <v>1356</v>
+      </c>
+      <c r="Q61" s="16" t="s">
         <v>1357</v>
-      </c>
-      <c r="Q61" s="16" t="s">
-        <v>1358</v>
       </c>
       <c r="R61" s="16" t="s">
         <v>1071</v>
@@ -17626,13 +17630,13 @@
         <v>454</v>
       </c>
       <c r="E62" s="16" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F62" s="16" t="s">
         <v>1359</v>
       </c>
-      <c r="F62" s="16" t="s">
+      <c r="G62" s="16" t="s">
         <v>1360</v>
-      </c>
-      <c r="G62" s="16" t="s">
-        <v>1361</v>
       </c>
       <c r="H62" s="16" t="s">
         <v>1079</v>
@@ -17644,10 +17648,10 @@
         <v>1080</v>
       </c>
       <c r="K62" s="16" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L62" s="16" t="s">
         <v>1362</v>
-      </c>
-      <c r="L62" s="16" t="s">
-        <v>1363</v>
       </c>
       <c r="M62" s="16" t="s">
         <v>1074</v>
@@ -17665,7 +17669,7 @@
         <v>1171</v>
       </c>
       <c r="R62" s="16" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -17678,25 +17682,25 @@
       <c r="C63" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="92" t="s">
         <v>457</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="16" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>1114</v>
       </c>
       <c r="H63" s="16"/>
       <c r="I63" s="16" t="s">
+        <v>1365</v>
+      </c>
+      <c r="J63" s="16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K63" s="16" t="s">
         <v>1366</v>
-      </c>
-      <c r="J63" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K63" s="16" t="s">
-        <v>1367</v>
       </c>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
@@ -17707,10 +17711,10 @@
         <v>1071</v>
       </c>
       <c r="P63" s="16" t="s">
+        <v>1367</v>
+      </c>
+      <c r="Q63" s="16" t="s">
         <v>1368</v>
-      </c>
-      <c r="Q63" s="16" t="s">
-        <v>1369</v>
       </c>
       <c r="R63" s="16" t="s">
         <v>1071</v>
@@ -17731,10 +17735,10 @@
       </c>
       <c r="E64" s="13"/>
       <c r="F64" s="16" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G64" s="16" t="s">
         <v>1370</v>
-      </c>
-      <c r="G64" s="16" t="s">
-        <v>1371</v>
       </c>
       <c r="H64" s="16" t="s">
         <v>1079</v>
@@ -17746,7 +17750,7 @@
         <v>1080</v>
       </c>
       <c r="K64" s="16" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
@@ -17760,7 +17764,7 @@
         <v>1071</v>
       </c>
       <c r="Q64" s="16" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="R64" s="16" t="s">
         <v>1071</v>
@@ -17781,10 +17785,10 @@
       </c>
       <c r="E65" s="13"/>
       <c r="F65" s="16" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G65" s="16" t="s">
         <v>1374</v>
-      </c>
-      <c r="G65" s="16" t="s">
-        <v>1375</v>
       </c>
       <c r="H65" s="16" t="s">
         <v>1079</v>
@@ -17796,7 +17800,7 @@
         <v>1080</v>
       </c>
       <c r="K65" s="16" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
@@ -17813,7 +17817,7 @@
         <v>1171</v>
       </c>
       <c r="R65" s="16" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -17826,12 +17830,12 @@
       <c r="C66" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="92" t="s">
         <v>461</v>
       </c>
       <c r="E66" s="13"/>
       <c r="F66" s="16" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>1249</v>
@@ -17850,7 +17854,7 @@
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
       <c r="O66" s="16" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="P66" s="16" t="s">
         <v>1249</v>
@@ -17872,25 +17876,25 @@
       <c r="C67" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="92" t="s">
         <v>457</v>
       </c>
       <c r="E67" s="13"/>
       <c r="F67" s="16" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="G67" s="16" t="s">
         <v>1114</v>
       </c>
       <c r="H67" s="16"/>
       <c r="I67" s="16" t="s">
+        <v>1380</v>
+      </c>
+      <c r="J67" s="16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K67" s="16" t="s">
         <v>1381</v>
-      </c>
-      <c r="J67" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K67" s="16" t="s">
-        <v>1382</v>
       </c>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
@@ -17901,10 +17905,10 @@
         <v>1071</v>
       </c>
       <c r="P67" s="16" t="s">
+        <v>1382</v>
+      </c>
+      <c r="Q67" s="16" t="s">
         <v>1383</v>
-      </c>
-      <c r="Q67" s="16" t="s">
-        <v>1384</v>
       </c>
       <c r="R67" s="16" t="s">
         <v>1071</v>
@@ -17920,12 +17924,12 @@
       <c r="C68" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="92" t="s">
         <v>461</v>
       </c>
       <c r="E68" s="13"/>
       <c r="F68" s="16" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G68" s="16" t="s">
         <v>1249</v>
@@ -17946,7 +17950,7 @@
         <v>1075</v>
       </c>
       <c r="O68" s="16" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="P68" s="16" t="s">
         <v>1249</v>
@@ -17968,25 +17972,25 @@
       <c r="C69" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="92" t="s">
         <v>457</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="16" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="G69" s="16" t="s">
         <v>1114</v>
       </c>
       <c r="H69" s="16"/>
       <c r="I69" s="16" t="s">
+        <v>1386</v>
+      </c>
+      <c r="J69" s="16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K69" s="16" t="s">
         <v>1387</v>
-      </c>
-      <c r="J69" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K69" s="16" t="s">
-        <v>1388</v>
       </c>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
@@ -18000,10 +18004,10 @@
         <v>1071</v>
       </c>
       <c r="Q69" s="16" t="s">
+        <v>1388</v>
+      </c>
+      <c r="R69" s="16" t="s">
         <v>1389</v>
-      </c>
-      <c r="R69" s="16" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="70" spans="1:18" s="33" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -18013,20 +18017,20 @@
       <c r="B70" s="34" t="s">
         <v>943</v>
       </c>
-      <c r="C70" s="92" t="s">
+      <c r="C70" s="89" t="s">
         <v>944</v>
       </c>
       <c r="D70" s="31" t="s">
         <v>448</v>
       </c>
       <c r="E70" s="32" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F70" s="32" t="s">
         <v>1391</v>
       </c>
-      <c r="F70" s="32" t="s">
+      <c r="G70" s="32" t="s">
         <v>1392</v>
-      </c>
-      <c r="G70" s="32" t="s">
-        <v>1393</v>
       </c>
       <c r="H70" s="32" t="s">
         <v>1079</v>
@@ -18038,10 +18042,10 @@
         <v>1080</v>
       </c>
       <c r="K70" s="32" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L70" s="32" t="s">
         <v>1394</v>
-      </c>
-      <c r="L70" s="32" t="s">
-        <v>1395</v>
       </c>
       <c r="M70" s="32" t="s">
         <v>1074</v>
@@ -18056,7 +18060,7 @@
         <v>1071</v>
       </c>
       <c r="Q70" s="32" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="R70" s="32" t="s">
         <v>1071</v>
@@ -18069,7 +18073,7 @@
       <c r="B71" s="34" t="s">
         <v>950</v>
       </c>
-      <c r="C71" s="92" t="s">
+      <c r="C71" s="89" t="s">
         <v>944</v>
       </c>
       <c r="D71" s="31" t="s">
@@ -18077,10 +18081,10 @@
       </c>
       <c r="E71" s="30"/>
       <c r="F71" s="32" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G71" s="32" t="s">
         <v>1397</v>
-      </c>
-      <c r="G71" s="32" t="s">
-        <v>1398</v>
       </c>
       <c r="H71" s="32" t="s">
         <v>1079</v>
@@ -18092,7 +18096,7 @@
         <v>1080</v>
       </c>
       <c r="K71" s="32" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="L71" s="31"/>
       <c r="M71" s="31"/>
@@ -18106,7 +18110,7 @@
         <v>1071</v>
       </c>
       <c r="Q71" s="32" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="R71" s="32" t="s">
         <v>1071</v>
@@ -18119,7 +18123,7 @@
       <c r="B72" s="34" t="s">
         <v>956</v>
       </c>
-      <c r="C72" s="92" t="s">
+      <c r="C72" s="89" t="s">
         <v>944</v>
       </c>
       <c r="D72" s="31" t="s">
@@ -18127,10 +18131,10 @@
       </c>
       <c r="E72" s="30"/>
       <c r="F72" s="32" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G72" s="32" t="s">
         <v>1401</v>
-      </c>
-      <c r="G72" s="32" t="s">
-        <v>1402</v>
       </c>
       <c r="H72" s="32" t="s">
         <v>1079</v>
@@ -18142,7 +18146,7 @@
         <v>1080</v>
       </c>
       <c r="K72" s="32" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="L72" s="31"/>
       <c r="M72" s="31"/>
@@ -18156,7 +18160,7 @@
         <v>1071</v>
       </c>
       <c r="Q72" s="32" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="R72" s="32" t="s">
         <v>1071</v>
@@ -18169,7 +18173,7 @@
       <c r="B73" s="34" t="s">
         <v>961</v>
       </c>
-      <c r="C73" s="92" t="s">
+      <c r="C73" s="89" t="s">
         <v>944</v>
       </c>
       <c r="D73" s="31" t="s">
@@ -18177,10 +18181,10 @@
       </c>
       <c r="E73" s="30"/>
       <c r="F73" s="32" t="s">
+        <v>1404</v>
+      </c>
+      <c r="G73" s="32" t="s">
         <v>1405</v>
-      </c>
-      <c r="G73" s="32" t="s">
-        <v>1406</v>
       </c>
       <c r="H73" s="32" t="s">
         <v>1079</v>
@@ -18192,7 +18196,7 @@
         <v>1080</v>
       </c>
       <c r="K73" s="32" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="L73" s="31"/>
       <c r="M73" s="31"/>
@@ -18206,7 +18210,7 @@
         <v>1071</v>
       </c>
       <c r="Q73" s="32" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="R73" s="32" t="s">
         <v>1071</v>
@@ -18226,13 +18230,13 @@
         <v>451</v>
       </c>
       <c r="E74" s="32" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F74" s="32" t="s">
         <v>1409</v>
       </c>
-      <c r="F74" s="32" t="s">
+      <c r="G74" s="32" t="s">
         <v>1410</v>
-      </c>
-      <c r="G74" s="32" t="s">
-        <v>1411</v>
       </c>
       <c r="H74" s="32" t="s">
         <v>1079</v>
@@ -18244,10 +18248,10 @@
         <v>1080</v>
       </c>
       <c r="K74" s="32" t="s">
+        <v>1411</v>
+      </c>
+      <c r="L74" s="32" t="s">
         <v>1412</v>
-      </c>
-      <c r="L74" s="32" t="s">
-        <v>1413</v>
       </c>
       <c r="M74" s="32" t="s">
         <v>1074</v>
@@ -18262,7 +18266,7 @@
         <v>1071</v>
       </c>
       <c r="Q74" s="32" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="R74" s="32" t="s">
         <v>1071</v>
@@ -18283,10 +18287,10 @@
       </c>
       <c r="E75" s="30"/>
       <c r="F75" s="32" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G75" s="32" t="s">
         <v>1415</v>
-      </c>
-      <c r="G75" s="32" t="s">
-        <v>1416</v>
       </c>
       <c r="H75" s="32" t="s">
         <v>1079</v>
@@ -18298,7 +18302,7 @@
         <v>1080</v>
       </c>
       <c r="K75" s="32" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="L75" s="31"/>
       <c r="M75" s="31"/>
@@ -18312,7 +18316,7 @@
         <v>1071</v>
       </c>
       <c r="Q75" s="32" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="R75" s="32" t="s">
         <v>1071</v>
@@ -18333,10 +18337,10 @@
       </c>
       <c r="E76" s="30"/>
       <c r="F76" s="32" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G76" s="32" t="s">
         <v>1419</v>
-      </c>
-      <c r="G76" s="32" t="s">
-        <v>1420</v>
       </c>
       <c r="H76" s="32" t="s">
         <v>1079</v>
@@ -18348,7 +18352,7 @@
         <v>1080</v>
       </c>
       <c r="K76" s="32" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="L76" s="31"/>
       <c r="M76" s="31"/>
@@ -18362,7 +18366,7 @@
         <v>1071</v>
       </c>
       <c r="Q76" s="32" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="R76" s="32" t="s">
         <v>1071</v>
@@ -18383,10 +18387,10 @@
       </c>
       <c r="E77" s="13"/>
       <c r="F77" s="16" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G77" s="16" t="s">
         <v>1423</v>
-      </c>
-      <c r="G77" s="16" t="s">
-        <v>1424</v>
       </c>
       <c r="H77" s="16" t="s">
         <v>1079</v>
@@ -18398,7 +18402,7 @@
         <v>1080</v>
       </c>
       <c r="K77" s="16" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
@@ -18412,7 +18416,7 @@
         <v>1071</v>
       </c>
       <c r="Q77" s="16" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="R77" s="16" t="s">
         <v>1071</v>
@@ -18433,10 +18437,10 @@
       </c>
       <c r="E78" s="13"/>
       <c r="F78" s="16" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G78" s="16" t="s">
         <v>1427</v>
-      </c>
-      <c r="G78" s="16" t="s">
-        <v>1428</v>
       </c>
       <c r="H78" s="16" t="s">
         <v>1079</v>
@@ -18448,7 +18452,7 @@
         <v>1080</v>
       </c>
       <c r="K78" s="16" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
@@ -18462,7 +18466,7 @@
         <v>1071</v>
       </c>
       <c r="Q78" s="16" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="R78" s="16" t="s">
         <v>1071</v>
@@ -18483,10 +18487,10 @@
       </c>
       <c r="E79" s="13"/>
       <c r="F79" s="16" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G79" s="16" t="s">
         <v>1431</v>
-      </c>
-      <c r="G79" s="16" t="s">
-        <v>1432</v>
       </c>
       <c r="H79" s="16" t="s">
         <v>1079</v>
@@ -18498,7 +18502,7 @@
         <v>1080</v>
       </c>
       <c r="K79" s="16" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
@@ -18512,7 +18516,7 @@
         <v>1071</v>
       </c>
       <c r="Q79" s="16" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="R79" s="16" t="s">
         <v>1071</v>
@@ -18533,10 +18537,10 @@
       </c>
       <c r="E80" s="13"/>
       <c r="F80" s="16" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G80" s="16" t="s">
         <v>1435</v>
-      </c>
-      <c r="G80" s="16" t="s">
-        <v>1436</v>
       </c>
       <c r="H80" s="16" t="s">
         <v>1079</v>
@@ -18548,7 +18552,7 @@
         <v>1080</v>
       </c>
       <c r="K80" s="16" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
@@ -18562,7 +18566,7 @@
         <v>1071</v>
       </c>
       <c r="Q80" s="16" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="R80" s="16" t="s">
         <v>1071</v>
@@ -18583,13 +18587,13 @@
       </c>
       <c r="E81" s="13"/>
       <c r="F81" s="16" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G81" s="16" t="s">
         <v>1439</v>
       </c>
-      <c r="G81" s="16" t="s">
-        <v>1440</v>
-      </c>
       <c r="H81" s="16" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="I81" s="16" t="s">
         <v>1071</v>
@@ -18598,7 +18602,7 @@
         <v>1080</v>
       </c>
       <c r="K81" s="16" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
@@ -18612,7 +18616,7 @@
         <v>1071</v>
       </c>
       <c r="Q81" s="16" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="R81" s="16" t="s">
         <v>1071</v>
@@ -18633,20 +18637,20 @@
       </c>
       <c r="E82" s="13"/>
       <c r="F82" s="16" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G82" s="16" t="s">
         <v>1114</v>
       </c>
       <c r="H82" s="16"/>
       <c r="I82" s="16" t="s">
+        <v>1443</v>
+      </c>
+      <c r="J82" s="16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K82" s="16" t="s">
         <v>1444</v>
-      </c>
-      <c r="J82" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K82" s="16" t="s">
-        <v>1445</v>
       </c>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
@@ -18660,7 +18664,7 @@
         <v>1071</v>
       </c>
       <c r="Q82" s="16" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="R82" s="16" t="s">
         <v>1071</v>
@@ -18681,10 +18685,10 @@
       </c>
       <c r="E83" s="13"/>
       <c r="F83" s="16" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G83" s="16" t="s">
         <v>1447</v>
-      </c>
-      <c r="G83" s="16" t="s">
-        <v>1448</v>
       </c>
       <c r="H83" s="16" t="s">
         <v>1079</v>
@@ -18696,7 +18700,7 @@
         <v>1080</v>
       </c>
       <c r="K83" s="16" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
@@ -18710,7 +18714,7 @@
         <v>1071</v>
       </c>
       <c r="Q83" s="16" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="R83" s="16" t="s">
         <v>1071</v>
@@ -18731,10 +18735,10 @@
       </c>
       <c r="E84" s="13"/>
       <c r="F84" s="16" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G84" s="16" t="s">
         <v>1451</v>
-      </c>
-      <c r="G84" s="16" t="s">
-        <v>1452</v>
       </c>
       <c r="H84" s="16" t="s">
         <v>1079</v>
@@ -18746,7 +18750,7 @@
         <v>1080</v>
       </c>
       <c r="K84" s="16" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
@@ -18760,7 +18764,7 @@
         <v>1071</v>
       </c>
       <c r="Q84" s="16" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="R84" s="16" t="s">
         <v>1071</v>
@@ -18781,10 +18785,10 @@
       </c>
       <c r="E85" s="13"/>
       <c r="F85" s="16" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G85" s="16" t="s">
         <v>1455</v>
-      </c>
-      <c r="G85" s="16" t="s">
-        <v>1456</v>
       </c>
       <c r="H85" s="16" t="s">
         <v>1079</v>
@@ -18796,7 +18800,7 @@
         <v>1080</v>
       </c>
       <c r="K85" s="16" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
@@ -18810,7 +18814,7 @@
         <v>1071</v>
       </c>
       <c r="Q85" s="16" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="R85" s="16" t="s">
         <v>1071</v>
@@ -18831,20 +18835,20 @@
       </c>
       <c r="E86" s="13"/>
       <c r="F86" s="16" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G86" s="16" t="s">
         <v>1114</v>
       </c>
       <c r="H86" s="16"/>
       <c r="I86" s="16" t="s">
+        <v>1459</v>
+      </c>
+      <c r="J86" s="16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K86" s="16" t="s">
         <v>1460</v>
-      </c>
-      <c r="J86" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K86" s="16" t="s">
-        <v>1461</v>
       </c>
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
@@ -18855,10 +18859,10 @@
         <v>1071</v>
       </c>
       <c r="P86" s="16" t="s">
+        <v>1461</v>
+      </c>
+      <c r="Q86" s="16" t="s">
         <v>1462</v>
-      </c>
-      <c r="Q86" s="16" t="s">
-        <v>1463</v>
       </c>
       <c r="R86" s="16" t="s">
         <v>1071</v>
@@ -18879,10 +18883,10 @@
       </c>
       <c r="E87" s="13"/>
       <c r="F87" s="16" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G87" s="16" t="s">
         <v>1464</v>
-      </c>
-      <c r="G87" s="16" t="s">
-        <v>1465</v>
       </c>
       <c r="H87" s="16" t="s">
         <v>1079</v>
@@ -18894,7 +18898,7 @@
         <v>1080</v>
       </c>
       <c r="K87" s="16" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
@@ -18908,7 +18912,7 @@
         <v>1071</v>
       </c>
       <c r="Q87" s="16" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="R87" s="16" t="s">
         <v>1071</v>
@@ -18929,10 +18933,10 @@
       </c>
       <c r="E88" s="13"/>
       <c r="F88" s="16" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G88" s="16" t="s">
         <v>1468</v>
-      </c>
-      <c r="G88" s="16" t="s">
-        <v>1469</v>
       </c>
       <c r="H88" s="16" t="s">
         <v>1079</v>
@@ -18944,7 +18948,7 @@
         <v>1080</v>
       </c>
       <c r="K88" s="16" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
@@ -18958,7 +18962,7 @@
         <v>1071</v>
       </c>
       <c r="Q88" s="16" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="R88" s="16" t="s">
         <v>1071</v>
@@ -18979,10 +18983,10 @@
       </c>
       <c r="E89" s="13"/>
       <c r="F89" s="16" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G89" s="16" t="s">
         <v>1472</v>
-      </c>
-      <c r="G89" s="16" t="s">
-        <v>1473</v>
       </c>
       <c r="H89" s="16" t="s">
         <v>1079</v>
@@ -18994,7 +18998,7 @@
         <v>1080</v>
       </c>
       <c r="K89" s="16" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
@@ -19008,7 +19012,7 @@
         <v>1071</v>
       </c>
       <c r="Q89" s="16" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="R89" s="16" t="s">
         <v>1071</v>
@@ -19029,20 +19033,20 @@
       </c>
       <c r="E90" s="13"/>
       <c r="F90" s="16" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="G90" s="16" t="s">
         <v>1114</v>
       </c>
       <c r="H90" s="16"/>
       <c r="I90" s="16" t="s">
+        <v>1476</v>
+      </c>
+      <c r="J90" s="16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K90" s="16" t="s">
         <v>1477</v>
-      </c>
-      <c r="J90" s="16" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K90" s="16" t="s">
-        <v>1478</v>
       </c>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
@@ -19056,10 +19060,10 @@
         <v>1071</v>
       </c>
       <c r="Q90" s="16" t="s">
+        <v>1478</v>
+      </c>
+      <c r="R90" s="16" t="s">
         <v>1479</v>
-      </c>
-      <c r="R90" s="16" t="s">
-        <v>1480</v>
       </c>
     </row>
   </sheetData>
